--- a/Assets/Excel/OrderData.xlsx
+++ b/Assets/Excel/OrderData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23535" windowHeight="10260"/>
+    <workbookView windowWidth="15825" windowHeight="9405"/>
   </bookViews>
   <sheets>
     <sheet name="OrderData" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,9 @@
     <t>rewardCoin</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -56,10 +59,7 @@
     <t>金元宝数量</t>
   </si>
   <si>
-    <t>银币数</t>
-  </si>
-  <si>
-    <t>int</t>
+    <t>铜币数</t>
   </si>
 </sst>
 </file>
@@ -675,9 +675,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1211,257 +1214,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>200</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>200</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>200</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>200</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>400</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>6</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>400</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>400</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>400</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>9</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>200</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>2</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>200</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14">
+      <c r="A14" s="1">
         <v>11</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>3</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>400</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>12</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>400</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>2000</v>
       </c>
     </row>
